--- a/notebooks/XGBoost/predictions_ele_2025.xlsx
+++ b/notebooks/XGBoost/predictions_ele_2025.xlsx
@@ -460,10 +460,10 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>69.50811004638672</v>
+        <v>69.50582122802734</v>
       </c>
       <c r="D2" t="n">
-        <v>68.81047058105469</v>
+        <v>68.74546051025391</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>67.73674774169922</v>
+        <v>67.72753143310547</v>
       </c>
       <c r="D3" t="n">
-        <v>67.87950897216797</v>
+        <v>67.85413360595703</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>70.33882141113281</v>
+        <v>70.32463836669922</v>
       </c>
       <c r="D4" t="n">
-        <v>69.28945159912109</v>
+        <v>69.36209869384766</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>70.96688079833984</v>
+        <v>70.92430114746094</v>
       </c>
       <c r="D5" t="n">
-        <v>69.7679443359375</v>
+        <v>69.78428649902344</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>72.47299957275391</v>
+        <v>72.44402313232422</v>
       </c>
       <c r="D6" t="n">
-        <v>70.51792144775391</v>
+        <v>70.51060485839844</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>70.71328735351562</v>
+        <v>70.70734405517578</v>
       </c>
       <c r="D7" t="n">
-        <v>69.62993621826172</v>
+        <v>69.60196685791016</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>70.32733154296875</v>
+        <v>70.33983612060547</v>
       </c>
       <c r="D8" t="n">
-        <v>69.35951232910156</v>
+        <v>69.33985900878906</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>72.32534027099609</v>
+        <v>72.33244323730469</v>
       </c>
       <c r="D9" t="n">
-        <v>70.42687225341797</v>
+        <v>70.43616485595703</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>70.67269897460938</v>
+        <v>70.74758148193359</v>
       </c>
       <c r="D10" t="n">
-        <v>69.63873291015625</v>
+        <v>69.61132049560547</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>71.64386749267578</v>
+        <v>71.62855529785156</v>
       </c>
       <c r="D11" t="n">
-        <v>70.09226989746094</v>
+        <v>70.08840179443359</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>67.58716583251953</v>
+        <v>67.63673400878906</v>
       </c>
       <c r="D12" t="n">
-        <v>67.87140655517578</v>
+        <v>67.88246154785156</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>72.13574981689453</v>
+        <v>72.12639617919922</v>
       </c>
       <c r="D13" t="n">
-        <v>70.27357482910156</v>
+        <v>70.29009246826172</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>69.87449645996094</v>
+        <v>69.91786193847656</v>
       </c>
       <c r="D14" t="n">
-        <v>68.91244506835938</v>
+        <v>69.08914184570312</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>68.67906188964844</v>
+        <v>68.68129730224609</v>
       </c>
       <c r="D15" t="n">
-        <v>68.54390716552734</v>
+        <v>68.48577117919922</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>75.22447204589844</v>
+        <v>75.28610229492188</v>
       </c>
       <c r="D16" t="n">
-        <v>72.03765869140625</v>
+        <v>72.11726379394531</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>72.54795837402344</v>
+        <v>72.56709289550781</v>
       </c>
       <c r="D17" t="n">
-        <v>70.50029754638672</v>
+        <v>70.63383483886719</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>71.79213714599609</v>
+        <v>71.80031585693359</v>
       </c>
       <c r="D18" t="n">
-        <v>70.09031677246094</v>
+        <v>70.17815399169922</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>68.73863983154297</v>
+        <v>68.72277069091797</v>
       </c>
       <c r="D19" t="n">
-        <v>68.51361846923828</v>
+        <v>68.50631713867188</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>74.87026977539062</v>
+        <v>74.86615753173828</v>
       </c>
       <c r="D20" t="n">
-        <v>71.60258483886719</v>
+        <v>71.60189819335938</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>69.10826873779297</v>
+        <v>69.11007690429688</v>
       </c>
       <c r="D21" t="n">
-        <v>68.64582824707031</v>
+        <v>68.66046905517578</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +780,10 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>70.66078948974609</v>
+        <v>70.58475494384766</v>
       </c>
       <c r="D22" t="n">
-        <v>69.57477569580078</v>
+        <v>69.56903839111328</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +796,10 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>69.60935211181641</v>
+        <v>69.55242156982422</v>
       </c>
       <c r="D23" t="n">
-        <v>68.81884765625</v>
+        <v>68.74776458740234</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +812,10 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>72.39864349365234</v>
+        <v>72.40657043457031</v>
       </c>
       <c r="D24" t="n">
-        <v>70.43692779541016</v>
+        <v>70.47873687744141</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +828,10 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>69.99823760986328</v>
+        <v>69.94329833984375</v>
       </c>
       <c r="D25" t="n">
-        <v>69.228271484375</v>
+        <v>69.17231750488281</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +844,10 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>68.98644256591797</v>
+        <v>69.00189208984375</v>
       </c>
       <c r="D26" t="n">
-        <v>68.36756896972656</v>
+        <v>68.49386596679688</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +860,10 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>70.83596801757812</v>
+        <v>70.88545989990234</v>
       </c>
       <c r="D27" t="n">
-        <v>69.63274383544922</v>
+        <v>69.74629974365234</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +876,10 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>73.30821990966797</v>
+        <v>73.31192016601562</v>
       </c>
       <c r="D28" t="n">
-        <v>70.93424224853516</v>
+        <v>70.98232269287109</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +892,10 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>71.08389282226562</v>
+        <v>71.12055206298828</v>
       </c>
       <c r="D29" t="n">
-        <v>69.76458740234375</v>
+        <v>69.79479217529297</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +908,10 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>68.2437744140625</v>
+        <v>68.21578979492188</v>
       </c>
       <c r="D30" t="n">
-        <v>68.41822814941406</v>
+        <v>68.41989898681641</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +924,10 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>73.43525695800781</v>
+        <v>73.46107482910156</v>
       </c>
       <c r="D31" t="n">
-        <v>71.15792846679688</v>
+        <v>71.17364501953125</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +940,10 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>69.33402252197266</v>
+        <v>69.26959991455078</v>
       </c>
       <c r="D32" t="n">
-        <v>68.81529235839844</v>
+        <v>68.83644104003906</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +956,10 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>69.82311248779297</v>
+        <v>69.76589202880859</v>
       </c>
       <c r="D33" t="n">
-        <v>69.21041107177734</v>
+        <v>69.18741607666016</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>70.87534332275391</v>
+        <v>70.84754943847656</v>
       </c>
       <c r="D34" t="n">
-        <v>69.72413635253906</v>
+        <v>69.64404296875</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>69.43471527099609</v>
+        <v>69.42791748046875</v>
       </c>
       <c r="D35" t="n">
-        <v>68.79782104492188</v>
+        <v>68.88604736328125</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +1004,10 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>70.93784332275391</v>
+        <v>70.91317749023438</v>
       </c>
       <c r="D36" t="n">
-        <v>69.7027587890625</v>
+        <v>69.73033905029297</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +1020,10 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>70.72098541259766</v>
+        <v>70.76008605957031</v>
       </c>
       <c r="D37" t="n">
-        <v>69.57354736328125</v>
+        <v>69.577392578125</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +1036,10 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>70.15605926513672</v>
+        <v>70.19414520263672</v>
       </c>
       <c r="D38" t="n">
-        <v>69.29025268554688</v>
+        <v>69.26214599609375</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +1052,10 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>70.28861999511719</v>
+        <v>70.35166168212891</v>
       </c>
       <c r="D39" t="n">
-        <v>69.35614013671875</v>
+        <v>69.36053466796875</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +1068,10 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>71.30925750732422</v>
+        <v>71.35294342041016</v>
       </c>
       <c r="D40" t="n">
-        <v>69.84974670410156</v>
+        <v>69.87619018554688</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +1084,10 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>69.84195709228516</v>
+        <v>69.91706848144531</v>
       </c>
       <c r="D41" t="n">
-        <v>69.06322479248047</v>
+        <v>69.14497375488281</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +1100,10 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>69.10550689697266</v>
+        <v>69.10301208496094</v>
       </c>
       <c r="D42" t="n">
-        <v>68.70266723632812</v>
+        <v>68.68000793457031</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +1116,10 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>68.592529296875</v>
+        <v>68.55364990234375</v>
       </c>
       <c r="D43" t="n">
-        <v>68.31859588623047</v>
+        <v>68.38003540039062</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1132,10 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>73.72636413574219</v>
+        <v>73.70972442626953</v>
       </c>
       <c r="D44" t="n">
-        <v>71.12947082519531</v>
+        <v>71.13058471679688</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1148,10 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>68.29789733886719</v>
+        <v>68.32606506347656</v>
       </c>
       <c r="D45" t="n">
-        <v>68.37641143798828</v>
+        <v>68.41085815429688</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1164,10 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>71.84527587890625</v>
+        <v>71.857421875</v>
       </c>
       <c r="D46" t="n">
-        <v>70.22937774658203</v>
+        <v>70.24707794189453</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1180,10 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>68.57734680175781</v>
+        <v>68.52753448486328</v>
       </c>
       <c r="D47" t="n">
-        <v>68.39494323730469</v>
+        <v>68.44687652587891</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1196,10 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>77.44563293457031</v>
+        <v>77.32974243164062</v>
       </c>
       <c r="D48" t="n">
-        <v>72.8892822265625</v>
+        <v>72.83051300048828</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1212,10 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>77.14621734619141</v>
+        <v>77.13526916503906</v>
       </c>
       <c r="D49" t="n">
-        <v>72.90139770507812</v>
+        <v>72.91859436035156</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1228,10 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>73.16099548339844</v>
+        <v>73.16263580322266</v>
       </c>
       <c r="D50" t="n">
-        <v>70.81791687011719</v>
+        <v>70.80137634277344</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1244,10 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>68.44931793212891</v>
+        <v>68.48641967773438</v>
       </c>
       <c r="D51" t="n">
-        <v>68.47669219970703</v>
+        <v>68.50276947021484</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1260,10 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>69.25196838378906</v>
+        <v>69.22694396972656</v>
       </c>
       <c r="D52" t="n">
-        <v>68.78844451904297</v>
+        <v>68.75727844238281</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1276,10 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>71.42623138427734</v>
+        <v>71.33269500732422</v>
       </c>
       <c r="D53" t="n">
-        <v>69.84996032714844</v>
+        <v>69.86209869384766</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1292,10 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>71.03048706054688</v>
+        <v>71.02104949951172</v>
       </c>
       <c r="D54" t="n">
-        <v>69.76959991455078</v>
+        <v>69.74759674072266</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1308,10 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>72.45082855224609</v>
+        <v>72.46018981933594</v>
       </c>
       <c r="D55" t="n">
-        <v>70.41131591796875</v>
+        <v>70.41778564453125</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1324,10 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>67.10199737548828</v>
+        <v>67.08310699462891</v>
       </c>
       <c r="D56" t="n">
-        <v>67.70582580566406</v>
+        <v>67.76161956787109</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1340,10 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>74.51811218261719</v>
+        <v>74.48655700683594</v>
       </c>
       <c r="D57" t="n">
-        <v>71.55368804931641</v>
+        <v>71.53181457519531</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1356,10 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>73.95146179199219</v>
+        <v>73.95069885253906</v>
       </c>
       <c r="D58" t="n">
-        <v>71.38457489013672</v>
+        <v>71.37217712402344</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1372,10 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>66.42049407958984</v>
+        <v>66.41677093505859</v>
       </c>
       <c r="D59" t="n">
-        <v>67.44296264648438</v>
+        <v>67.38610076904297</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1388,10 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>69.66925811767578</v>
+        <v>69.671142578125</v>
       </c>
       <c r="D60" t="n">
-        <v>68.96542358398438</v>
+        <v>68.95316314697266</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1404,10 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>71.85098266601562</v>
+        <v>71.88488006591797</v>
       </c>
       <c r="D61" t="n">
-        <v>70.13058471679688</v>
+        <v>70.10361480712891</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1420,10 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>71.40920257568359</v>
+        <v>71.40813446044922</v>
       </c>
       <c r="D62" t="n">
-        <v>69.89521026611328</v>
+        <v>69.88832855224609</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1436,10 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>71.39365386962891</v>
+        <v>71.37287139892578</v>
       </c>
       <c r="D63" t="n">
-        <v>69.88730621337891</v>
+        <v>69.89664459228516</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1452,10 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>71.76992034912109</v>
+        <v>71.80502319335938</v>
       </c>
       <c r="D64" t="n">
-        <v>70.09707641601562</v>
+        <v>70.06240844726562</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1468,10 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>69.36676788330078</v>
+        <v>69.42814636230469</v>
       </c>
       <c r="D65" t="n">
-        <v>68.81526184082031</v>
+        <v>68.9283447265625</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1484,10 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>70.82325744628906</v>
+        <v>70.82427215576172</v>
       </c>
       <c r="D66" t="n">
-        <v>69.67567443847656</v>
+        <v>69.64823913574219</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1500,10 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>69.91110229492188</v>
+        <v>69.94975280761719</v>
       </c>
       <c r="D67" t="n">
-        <v>68.98495483398438</v>
+        <v>69.03211212158203</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1516,10 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>73.77989196777344</v>
+        <v>73.78632354736328</v>
       </c>
       <c r="D68" t="n">
-        <v>71.21525573730469</v>
+        <v>71.17801666259766</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1532,10 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>71.34531402587891</v>
+        <v>71.56301116943359</v>
       </c>
       <c r="D69" t="n">
-        <v>69.88922882080078</v>
+        <v>69.90121459960938</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1548,10 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>69.33023071289062</v>
+        <v>69.37889099121094</v>
       </c>
       <c r="D70" t="n">
-        <v>68.71254730224609</v>
+        <v>68.70515441894531</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1564,10 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>71.70774841308594</v>
+        <v>71.70955657958984</v>
       </c>
       <c r="D71" t="n">
-        <v>70.15011596679688</v>
+        <v>70.14913940429688</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1580,10 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>71.02065277099609</v>
+        <v>70.96221160888672</v>
       </c>
       <c r="D72" t="n">
-        <v>69.82115936279297</v>
+        <v>69.75470733642578</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1596,10 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>73.9169921875</v>
+        <v>73.91098785400391</v>
       </c>
       <c r="D73" t="n">
-        <v>71.32454681396484</v>
+        <v>71.31417083740234</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1612,10 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>71.24604034423828</v>
+        <v>71.23155212402344</v>
       </c>
       <c r="D74" t="n">
-        <v>69.80344390869141</v>
+        <v>69.88452911376953</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1628,10 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>70.65619659423828</v>
+        <v>70.74993896484375</v>
       </c>
       <c r="D75" t="n">
-        <v>69.56024932861328</v>
+        <v>69.56217956542969</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1644,10 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>69.25694274902344</v>
+        <v>69.30863952636719</v>
       </c>
       <c r="D76" t="n">
-        <v>68.83458709716797</v>
+        <v>68.77548980712891</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1660,10 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>74.80502319335938</v>
+        <v>74.78513336181641</v>
       </c>
       <c r="D77" t="n">
-        <v>71.70027923583984</v>
+        <v>71.73542785644531</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1676,10 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>71.27490234375</v>
+        <v>71.26811218261719</v>
       </c>
       <c r="D78" t="n">
-        <v>69.82396697998047</v>
+        <v>69.85778045654297</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1692,10 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>74.58694458007812</v>
+        <v>74.57771301269531</v>
       </c>
       <c r="D79" t="n">
-        <v>71.65462493896484</v>
+        <v>71.59365844726562</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1708,10 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>71.78860473632812</v>
+        <v>71.80317687988281</v>
       </c>
       <c r="D80" t="n">
-        <v>70.22027587890625</v>
+        <v>70.22125244140625</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1724,10 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>65.42494964599609</v>
+        <v>65.39945220947266</v>
       </c>
       <c r="D81" t="n">
-        <v>67.02417755126953</v>
+        <v>66.70315551757812</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1740,10 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>73.80522918701172</v>
+        <v>73.81201171875</v>
       </c>
       <c r="D82" t="n">
-        <v>71.4293212890625</v>
+        <v>71.42749786376953</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1756,10 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>70.73366546630859</v>
+        <v>70.68827056884766</v>
       </c>
       <c r="D83" t="n">
-        <v>69.62057495117188</v>
+        <v>69.60364532470703</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1772,10 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>76.73368835449219</v>
+        <v>76.80142211914062</v>
       </c>
       <c r="D84" t="n">
-        <v>72.79343414306641</v>
+        <v>72.75776672363281</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1788,10 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>75.03580474853516</v>
+        <v>75.06707000732422</v>
       </c>
       <c r="D85" t="n">
-        <v>71.91884613037109</v>
+        <v>71.93696594238281</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1804,10 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>74.50277709960938</v>
+        <v>74.50986480712891</v>
       </c>
       <c r="D86" t="n">
-        <v>71.55155944824219</v>
+        <v>71.57210540771484</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_ele_2025.xlsx
+++ b/notebooks/XGBoost/predictions_ele_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predictions</t>
+          <t>ОПЖ_прогноз</t>
         </is>
       </c>
     </row>
@@ -460,10 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>69.50582122802734</v>
-      </c>
-      <c r="D2" t="n">
-        <v>68.74546051025391</v>
+        <v>69.37892913818359</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>67.72753143310547</v>
-      </c>
-      <c r="D3" t="n">
-        <v>67.85413360595703</v>
+        <v>67.19337463378906</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>70.32463836669922</v>
-      </c>
-      <c r="D4" t="n">
-        <v>69.36209869384766</v>
+        <v>70.10077667236328</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>70.92430114746094</v>
-      </c>
-      <c r="D5" t="n">
-        <v>69.78428649902344</v>
+        <v>70.71748352050781</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +507,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>72.44402313232422</v>
-      </c>
-      <c r="D6" t="n">
-        <v>70.51060485839844</v>
+        <v>72.40522766113281</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>70.70734405517578</v>
-      </c>
-      <c r="D7" t="n">
-        <v>69.60196685791016</v>
+        <v>70.35142517089844</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +533,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>70.33983612060547</v>
-      </c>
-      <c r="D8" t="n">
-        <v>69.33985900878906</v>
+        <v>70.05351257324219</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33244323730469</v>
-      </c>
-      <c r="D9" t="n">
-        <v>70.43616485595703</v>
+        <v>72.30374908447266</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>70.74758148193359</v>
-      </c>
-      <c r="D10" t="n">
-        <v>69.61132049560547</v>
+        <v>70.25669860839844</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>71.62855529785156</v>
-      </c>
-      <c r="D11" t="n">
-        <v>70.08840179443359</v>
+        <v>71.28793334960938</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>67.63673400878906</v>
-      </c>
-      <c r="D12" t="n">
-        <v>67.88246154785156</v>
+        <v>67.58062744140625</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>72.12639617919922</v>
-      </c>
-      <c r="D13" t="n">
-        <v>70.29009246826172</v>
+        <v>72.04278564453125</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +611,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>69.91786193847656</v>
-      </c>
-      <c r="D14" t="n">
-        <v>69.08914184570312</v>
+        <v>69.67334747314453</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>68.68129730224609</v>
-      </c>
-      <c r="D15" t="n">
-        <v>68.48577117919922</v>
+        <v>68.53907775878906</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>75.28610229492188</v>
-      </c>
-      <c r="D16" t="n">
-        <v>72.11726379394531</v>
+        <v>75.49141693115234</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>72.56709289550781</v>
-      </c>
-      <c r="D17" t="n">
-        <v>70.63383483886719</v>
+        <v>72.42258453369141</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +663,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>71.80031585693359</v>
-      </c>
-      <c r="D18" t="n">
-        <v>70.17815399169922</v>
+        <v>71.91667175292969</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>68.72277069091797</v>
-      </c>
-      <c r="D19" t="n">
-        <v>68.50631713867188</v>
+        <v>69.08393859863281</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>74.86615753173828</v>
-      </c>
-      <c r="D20" t="n">
-        <v>71.60189819335938</v>
+        <v>74.44746398925781</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>69.11007690429688</v>
-      </c>
-      <c r="D21" t="n">
-        <v>68.66046905517578</v>
+        <v>69.01384735107422</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +715,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>70.58475494384766</v>
-      </c>
-      <c r="D22" t="n">
-        <v>69.56903839111328</v>
+        <v>70.35203552246094</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>69.55242156982422</v>
-      </c>
-      <c r="D23" t="n">
-        <v>68.74776458740234</v>
+        <v>69.72552490234375</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>72.40657043457031</v>
-      </c>
-      <c r="D24" t="n">
-        <v>70.47873687744141</v>
+        <v>72.38315582275391</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>69.94329833984375</v>
-      </c>
-      <c r="D25" t="n">
-        <v>69.17231750488281</v>
+        <v>69.82456970214844</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>69.00189208984375</v>
-      </c>
-      <c r="D26" t="n">
-        <v>68.49386596679688</v>
+        <v>68.38883209228516</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>70.88545989990234</v>
-      </c>
-      <c r="D27" t="n">
-        <v>69.74629974365234</v>
+        <v>71.04766082763672</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>73.31192016601562</v>
-      </c>
-      <c r="D28" t="n">
-        <v>70.98232269287109</v>
+        <v>73.77132415771484</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>71.12055206298828</v>
-      </c>
-      <c r="D29" t="n">
-        <v>69.79479217529297</v>
+        <v>71.01043701171875</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>68.21578979492188</v>
-      </c>
-      <c r="D30" t="n">
-        <v>68.41989898681641</v>
+        <v>67.95652008056641</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +832,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>73.46107482910156</v>
-      </c>
-      <c r="D31" t="n">
-        <v>71.17364501953125</v>
+        <v>73.18948364257812</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>69.26959991455078</v>
-      </c>
-      <c r="D32" t="n">
-        <v>68.83644104003906</v>
+        <v>69.05126190185547</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>69.76589202880859</v>
-      </c>
-      <c r="D33" t="n">
-        <v>69.18741607666016</v>
+        <v>69.43852996826172</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>70.84754943847656</v>
-      </c>
-      <c r="D34" t="n">
-        <v>69.64404296875</v>
+        <v>70.47000122070312</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>69.42791748046875</v>
-      </c>
-      <c r="D35" t="n">
-        <v>68.88604736328125</v>
+        <v>69.05959320068359</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>70.91317749023438</v>
-      </c>
-      <c r="D36" t="n">
-        <v>69.73033905029297</v>
+        <v>70.78482055664062</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>70.76008605957031</v>
-      </c>
-      <c r="D37" t="n">
-        <v>69.577392578125</v>
+        <v>70.34812164306641</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>70.19414520263672</v>
-      </c>
-      <c r="D38" t="n">
-        <v>69.26214599609375</v>
+        <v>69.65404510498047</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>70.35166168212891</v>
-      </c>
-      <c r="D39" t="n">
-        <v>69.36053466796875</v>
+        <v>69.96212768554688</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>71.35294342041016</v>
-      </c>
-      <c r="D40" t="n">
-        <v>69.87619018554688</v>
+        <v>70.98749542236328</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>69.91706848144531</v>
-      </c>
-      <c r="D41" t="n">
-        <v>69.14497375488281</v>
+        <v>69.46751403808594</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +975,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>69.10301208496094</v>
-      </c>
-      <c r="D42" t="n">
-        <v>68.68000793457031</v>
+        <v>68.87757873535156</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>68.55364990234375</v>
-      </c>
-      <c r="D43" t="n">
-        <v>68.38003540039062</v>
+        <v>68.62844848632812</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>73.70972442626953</v>
-      </c>
-      <c r="D44" t="n">
-        <v>71.13058471679688</v>
+        <v>74.14470672607422</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>68.32606506347656</v>
-      </c>
-      <c r="D45" t="n">
-        <v>68.41085815429688</v>
+        <v>67.85957336425781</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1027,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>71.857421875</v>
-      </c>
-      <c r="D46" t="n">
-        <v>70.24707794189453</v>
+        <v>72.12035369873047</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>68.52753448486328</v>
-      </c>
-      <c r="D47" t="n">
-        <v>68.44687652587891</v>
+        <v>68.06734466552734</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>77.32974243164062</v>
-      </c>
-      <c r="D48" t="n">
-        <v>72.83051300048828</v>
+        <v>76.42304229736328</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>77.13526916503906</v>
-      </c>
-      <c r="D49" t="n">
-        <v>72.91859436035156</v>
+        <v>76.28598785400391</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>73.16263580322266</v>
-      </c>
-      <c r="D50" t="n">
-        <v>70.80137634277344</v>
+        <v>73.18026733398438</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1092,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>68.48641967773438</v>
-      </c>
-      <c r="D51" t="n">
-        <v>68.50276947021484</v>
+        <v>68.47787475585938</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1105,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>69.22694396972656</v>
-      </c>
-      <c r="D52" t="n">
-        <v>68.75727844238281</v>
+        <v>68.94472503662109</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>71.33269500732422</v>
-      </c>
-      <c r="D53" t="n">
-        <v>69.86209869384766</v>
+        <v>71.15592956542969</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>71.02104949951172</v>
-      </c>
-      <c r="D54" t="n">
-        <v>69.74759674072266</v>
+        <v>70.46086120605469</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1144,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>72.46018981933594</v>
-      </c>
-      <c r="D55" t="n">
-        <v>70.41778564453125</v>
+        <v>72.5693359375</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>67.08310699462891</v>
-      </c>
-      <c r="D56" t="n">
-        <v>67.76161956787109</v>
+        <v>66.51954650878906</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>74.48655700683594</v>
-      </c>
-      <c r="D57" t="n">
-        <v>71.53181457519531</v>
+        <v>74.42307281494141</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>73.95069885253906</v>
-      </c>
-      <c r="D58" t="n">
-        <v>71.37217712402344</v>
+        <v>74.10157775878906</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1196,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>66.41677093505859</v>
-      </c>
-      <c r="D59" t="n">
-        <v>67.38610076904297</v>
+        <v>66.16810607910156</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>69.671142578125</v>
-      </c>
-      <c r="D60" t="n">
-        <v>68.95316314697266</v>
+        <v>69.36856842041016</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>71.88488006591797</v>
-      </c>
-      <c r="D61" t="n">
-        <v>70.10361480712891</v>
+        <v>72.21504974365234</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1235,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>71.40813446044922</v>
-      </c>
-      <c r="D62" t="n">
-        <v>69.88832855224609</v>
+        <v>71.78346252441406</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>71.37287139892578</v>
-      </c>
-      <c r="D63" t="n">
-        <v>69.89664459228516</v>
+        <v>71.02156066894531</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1261,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>71.80502319335938</v>
-      </c>
-      <c r="D64" t="n">
-        <v>70.06240844726562</v>
+        <v>72.07838439941406</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>69.42814636230469</v>
-      </c>
-      <c r="D65" t="n">
-        <v>68.9283447265625</v>
+        <v>68.99634552001953</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1287,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>70.82427215576172</v>
-      </c>
-      <c r="D66" t="n">
-        <v>69.64823913574219</v>
+        <v>70.45574951171875</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1300,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>69.94975280761719</v>
-      </c>
-      <c r="D67" t="n">
-        <v>69.03211212158203</v>
+        <v>69.97441864013672</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>73.78632354736328</v>
-      </c>
-      <c r="D68" t="n">
-        <v>71.17801666259766</v>
+        <v>73.87499237060547</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>71.56301116943359</v>
-      </c>
-      <c r="D69" t="n">
-        <v>69.90121459960938</v>
+        <v>70.99716949462891</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1339,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>69.37889099121094</v>
-      </c>
-      <c r="D70" t="n">
-        <v>68.70515441894531</v>
+        <v>69.25255584716797</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>71.70955657958984</v>
-      </c>
-      <c r="D71" t="n">
-        <v>70.14913940429688</v>
+        <v>71.48426818847656</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>70.96221160888672</v>
-      </c>
-      <c r="D72" t="n">
-        <v>69.75470733642578</v>
+        <v>70.61322021484375</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>73.91098785400391</v>
-      </c>
-      <c r="D73" t="n">
-        <v>71.31417083740234</v>
+        <v>74.14887237548828</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>71.23155212402344</v>
-      </c>
-      <c r="D74" t="n">
-        <v>69.88452911376953</v>
+        <v>71.09175109863281</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>70.74993896484375</v>
-      </c>
-      <c r="D75" t="n">
-        <v>69.56217956542969</v>
+        <v>70.42611694335938</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1417,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>69.30863952636719</v>
-      </c>
-      <c r="D76" t="n">
-        <v>68.77548980712891</v>
+        <v>68.98708343505859</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1430,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>74.78513336181641</v>
-      </c>
-      <c r="D77" t="n">
-        <v>71.73542785644531</v>
+        <v>74.59089660644531</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>71.26811218261719</v>
-      </c>
-      <c r="D78" t="n">
-        <v>69.85778045654297</v>
+        <v>71.03107452392578</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1456,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>74.57771301269531</v>
-      </c>
-      <c r="D79" t="n">
-        <v>71.59365844726562</v>
+        <v>74.53115081787109</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1469,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>71.80317687988281</v>
-      </c>
-      <c r="D80" t="n">
-        <v>70.22125244140625</v>
+        <v>71.68321228027344</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>65.39945220947266</v>
-      </c>
-      <c r="D81" t="n">
-        <v>66.70315551757812</v>
+        <v>65.41876983642578</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>73.81201171875</v>
-      </c>
-      <c r="D82" t="n">
-        <v>71.42749786376953</v>
+        <v>73.83020782470703</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>70.68827056884766</v>
-      </c>
-      <c r="D83" t="n">
-        <v>69.60364532470703</v>
+        <v>70.47306060791016</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>76.80142211914062</v>
-      </c>
-      <c r="D84" t="n">
-        <v>72.75776672363281</v>
+        <v>76.02309417724609</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>75.06707000732422</v>
-      </c>
-      <c r="D85" t="n">
-        <v>71.93696594238281</v>
+        <v>74.54074859619141</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>74.50986480712891</v>
-      </c>
-      <c r="D86" t="n">
-        <v>71.57210540771484</v>
+        <v>74.43679809570312</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_ele_2025.xlsx
+++ b/notebooks/XGBoost/predictions_ele_2025.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
     </row>
